--- a/digital_mkt_250715/Kurly_reviews.xlsx
+++ b/digital_mkt_250715/Kurly_reviews.xlsx
@@ -413,13 +413,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
           <t>리뷰 내용</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>리뷰 번호</t>
         </is>
       </c>
     </row>
@@ -486,49 +491,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>알이 크고 신선해서 자주 구매해요</t>
+          <t>알 크기가 크고 깨지지 않게 도착해서 다행이에요~ 신선해요!</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>계란 신선해서 항상 사요</t>
+          <t>매번 주문하는 계란이에요 퀄리티 좋아요!</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>꼼꼼하게 포장되어 있어서 좋네요. 계란은 자주 구매 중인 제품이라 좋아요</t>
+          <t>신선해요
+주기적 구매템</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>계란은 웬만해선 컬리에서 사요 엄마집에도 보내드렸더니 좋아하시더라구요</t>
+          <t>살 짝   작다는 느낌  ...</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>역시 겨란은 컬리가 신선</t>
+          <t>컬리계란은 항상 믿고 먹어요</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>자주사는 계란이에요</t>
+          <t>노른자가 탱탱합니다. 너무 맛있어요. 믿고 구매요</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>부숴진 것 없이 꺠끗하게 잘 배송왔어요</t>
+          <t>싱싱하고 좋아요 강추</t>
         </is>
       </c>
     </row>
